--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,12 @@
       <name val="Microsoft JhengHei"/>
       <b val="1"/>
       <color rgb="0017202B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="0017202B"/>
       <sz val="14"/>
     </font>
   </fonts>
@@ -83,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -104,6 +110,50 @@
       <bottom style="thin">
         <color rgb="00C9CED6"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9CED6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9CED6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9CED6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9CED6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9CED6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9CED6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9CED6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9CED6"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -142,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,14 +215,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -538,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1146,12 +1199,111 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>參與人</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>負責</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>項目負責人；軟件開發</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>統籌時間表，對接玩具廠、電路板供應商和客戶；開發網頁、後台、語音系統、韌體、Tool call 和 RAG，部署三套系統；負責測試和 UAT</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>設計</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>三套 UI／UX 設計；角色和內容（人設、說話風格、開場白、聲線、角色圖）；App 圖示、啟動畫面和商店截圖</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>App 殼</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；和 Jacky 定網頁對接方式；出測試版，提交蘋果和 Google 審核並上架</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="12">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1176,16 +1328,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>軟件開發與測試：網頁、App、Tool call、RAG、後台、測試、UAT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>網頁 App 包在原生殼裡，1/15 上架快活和政協青年聯會兩個 App（AI Buddy 隨玩具延後）。殼由 Neo 負責；設計、角色和 App 圖由 Navy 負責；「我方軟件」是網頁、後台、語音系統和韌體。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>網頁 App 包在原生殼裡，1/15 上架快活和政協青年聯會兩個 App（AI Buddy 隨玩具延後）。殼由 Neo 負責；設計、角色和 App 圖由 Navy 負責；網頁、後台、語音系統和韌體由 Jacky 負責。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1374,7 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>設計</t>
         </is>
@@ -1232,7 +1384,7 @@
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>10/23</t>
         </is>
@@ -1254,13 +1406,13 @@
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="12" t="n"/>
+      <c r="A6" s="15" t="n"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>W2–W4</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
@@ -1281,21 +1433,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="12" t="n"/>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="15" t="n"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>W2–W5</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>11/13</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Navy；我方軟件放進系統</t>
+          <t>Navy；Jacky 放進系統</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1310,13 +1462,13 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="13" t="n"/>
+      <c r="A8" s="16" t="n"/>
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>W6–W7</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
@@ -1338,7 +1490,7 @@
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>網頁</t>
         </is>
@@ -1348,14 +1500,14 @@
           <t>W1–W3</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1370,20 +1522,20 @@
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="12" t="n"/>
+      <c r="A10" s="15" t="n"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>W3–W4</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1398,20 +1550,20 @@
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="12" t="n"/>
+      <c r="A11" s="15" t="n"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>W4–W6</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1426,20 +1578,20 @@
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="13" t="n"/>
+      <c r="A12" s="16" t="n"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1454,7 +1606,7 @@
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>App 殼與上架</t>
         </is>
@@ -1464,14 +1616,14 @@
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>10/23</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Neo、我方軟件</t>
+          <t>Neo、Jacky</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1486,13 +1638,13 @@
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="12" t="n"/>
+      <c r="A14" s="15" t="n"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>W3–W6</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
@@ -1514,13 +1666,13 @@
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="12" t="n"/>
+      <c r="A15" s="15" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>W8–W9</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>12/11</t>
         </is>
@@ -1542,13 +1694,13 @@
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="13" t="n"/>
+      <c r="A16" s="16" t="n"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>1/15</t>
         </is>
@@ -1570,7 +1722,7 @@
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Tool call</t>
         </is>
@@ -1580,14 +1732,14 @@
           <t>W2–W3</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1602,20 +1754,20 @@
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="13" t="n"/>
+      <c r="A18" s="16" t="n"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>W4–W6</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1629,8 +1781,8 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>RAG 知識庫（快活）</t>
         </is>
@@ -1640,14 +1792,14 @@
           <t>W4</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>馬會提供資料；我方軟件</t>
+          <t>馬會提供資料；Jacky</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1662,20 +1814,20 @@
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="12" t="n"/>
+      <c r="A20" s="15" t="n"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>W5–W8</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1689,21 +1841,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="13" t="n"/>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="16" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>W9–W11</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>12/25</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>馬會審核；我方軟件修改</t>
+          <t>馬會審核；Jacky 修改</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1718,7 +1870,7 @@
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>後台管理</t>
         </is>
@@ -1728,14 +1880,14 @@
           <t>W3–W6</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1750,20 +1902,20 @@
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="13" t="n"/>
+      <c r="A23" s="16" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>W6–W8</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1778,7 +1930,7 @@
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>測試</t>
         </is>
@@ -1788,14 +1940,14 @@
           <t>W4–W7</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>我方全體</t>
+          <t>全體</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1810,20 +1962,20 @@
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="13" t="n"/>
+      <c r="A25" s="16" t="n"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>W7–W8</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1838,7 +1990,7 @@
       </c>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
@@ -1848,14 +2000,14 @@
           <t>W9–W10</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>12/18</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>馬會、政協青年聯會；我方</t>
+          <t>馬會、政協青年聯會；Jacky</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1870,20 +2022,20 @@
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="13" t="n"/>
+      <c r="A27" s="16" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>我方軟件</t>
+          <t>Jacky</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -715,12 +715,12 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>審 3D 圖；決定電路板改不改；和 Neo 定好 App 殼和網頁的對接方式；Navy 出 UI／UX 設計方向</t>
+          <t>審 3D 圖；決定電路板改不改；Jacky 把 App 接口參數交給 Neo；Navy 出 UI／UX 設計方向</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；對接清單由 Neo 確認；設計方向交客戶</t>
+          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；接口參數 Neo 確認可以開發；設計方向交客戶</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1241,14 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>統籌時間表，對接玩具廠、電路板供應商和客戶；開發網頁、後台、語音系統、韌體、Tool call 和 RAG，部署三套系統；負責測試和 UAT</t>
+          <t>統籌時間表，對接玩具廠、電路板供應商和客戶；開發網頁（把 Navy 的設計圖做進 App 畫面）、後台、語音系統、韌體、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；負責測試和 UAT</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="10" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Navy</t>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>三套 UI／UX 設計；角色和內容（人設、說話風格、開場白、聲線、角色圖）；App 圖示、啟動畫面和商店截圖</t>
+          <t>三套 UI／UX 設計；角色和內容（人設、說話風格、開場白、聲線、角色圖）；App 設計圖、圖示、啟動畫面和商店截圖，全部交給 Jacky</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；和 Jacky 定網頁對接方式；出測試版，提交蘋果和 Google 審核並上架</t>
+          <t>按 Jacky 給的接口參數，開發 iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；出測試版，提交蘋果和 Google 審核並上架</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>Navy → Jacky</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>配網、綁定、首頁、對話、記憶、設定、語言等頁面的設計稿可以直接開發；政協青年聯會版只換顏色、logo、插圖；客戶確認</t>
+          <t>配網、綁定、首頁、對話、記憶、設定、語言等頁面的設計稿和切圖交給 Jacky，可以直接做進網頁；政協青年聯會版只換顏色、logo、插圖；客戶確認</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Navy → Neo</t>
+          <t>Navy → Jacky</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>兩個 App 的圖示、啟動畫面、商店截圖和宣傳圖，按蘋果和 Google 的尺寸交給 Neo</t>
+          <t>兩個 App 的圖示、啟動畫面、商店截圖和宣傳圖，按蘋果和 Google 的尺寸交給 Jacky</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>App 殼與上架</t>
@@ -1623,17 +1623,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Neo、Jacky</t>
+          <t>Jacky → Neo</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>網頁和殼的對接方案</t>
+          <t>Jacky 交 App 接口參數給 Neo</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>對接清單（藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結）逐項寫明介面和錯誤，Neo 書面確認；兩個 App 的名稱、圖示、bundle id 定好</t>
+          <t>接口文件交給 Neo：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；Neo 確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>殼開發、測試版</t>
+          <t>按接口參數開發殼、出測試版</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -1241,7 +1241,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>統籌時間表，對接玩具廠、電路板供應商和客戶；開發網頁（把 Navy 的設計圖做進 App 畫面）、後台、語音系統、韌體、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；負責測試和 UAT</t>
+          <t>統籌時間表，對接玩具廠、電路板供應商和客戶；統一開發一套網頁、三套外觀（把 Navy 的設計圖做進 App 畫面）、後台、語音系統、韌體、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；負責測試和 UAT</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -1337,7 +1337,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>網頁 App 包在原生殼裡，1/15 上架快活和政協青年聯會兩個 App（AI Buddy 隨玩具延後）。殼由 Neo 負責；設計、角色和 App 圖由 Navy 負責；網頁、後台、語音系統和韌體由 Jacky 負責。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
+          <t>網頁統一開發一套，三個品牌是三套外觀，包在原生殼裡；1/15 上架快活和政協青年聯會兩個 App（AI Buddy 隨玩具延後）。殼由 Neo 負責；設計、角色和 App 圖由 Navy 負責；網頁、後台、語音系統和韌體由 Jacky 負責。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="88" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>網頁</t>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>共用基礎：品牌主題、App 內登入、刪除帳號</t>
+          <t>統一開發一套網頁，三套外觀；App 內登入、刪除帳號</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>快活、政協青年聯會的顏色、logo、文案顯示正確，畫面不閃；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
+          <t>同一套程式碼按設定切換三套外觀（快活、政協青年聯會、AI Buddy）：顏色、字體、logo、圖示、文案；共用元件裡沒有寫死的品牌；加一套外觀不用改程式；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>快活專屬功能；政協青年聯會換主題</t>
+          <t>快活的功能開關；政協青年聯會套用外觀</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版：共用快活的成人版流程，只換顏色、logo、文案和角色</t>
+          <t>同一套網頁裡打開快活的功能：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版用同一套成人版流程，只換外觀和角色</t>
         </is>
       </c>
     </row>

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1">
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>W1</t>
@@ -682,7 +682,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>定下全部 IP 造型交玩具廠（目前只交了馬會）；交機芯規格；向電路板供應商詢價、追加樣板</t>
+          <t>Navy 完成政協青年聯會版的 IP 造型設計，交玩具廠（馬會的已交）；交機芯規格；向電路板供應商詢價、追加樣板</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>裝板實測，給修改意見；電路板定案；App 登入和品牌主題</t>
+          <t>裝板實測，給修改意見；Navy 給外觀意見；電路板定案；App 登入和品牌主題</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1248,7 +1248,7 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="10" t="n"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="56" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Navy</t>
@@ -1257,12 +1257,12 @@
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>設計</t>
+          <t>設計（IP 造型、UI／UX、角色）</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>三套 UI／UX 設計；角色和內容（人設、說話風格、開場白、聲線、角色圖）；App 設計圖、圖示、啟動畫面和商店截圖，全部交給 Jacky</t>
+          <t>IP 造型設計（政協青年聯會版等），跟進打樣外觀到簽樣；三套 UI／UX 設計；角色和內容（人設、說話風格、開場白、聲線、角色圖）；App 設計圖、圖示、啟動畫面和商店截圖，全部交給 Jacky</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -1316,7 +1316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1381,375 +1381,371 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>W1–W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10/23</t>
+          <t>10/16</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>Navy → 玩具廠</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>三套 UI／UX 設計方向</t>
+          <t>IP 造型設計</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>快活、政協青年聯會、AI Buddy 各一份設計規範（顏色、字體、圖示、按鈕）和主要頁面線框；快活和政協青年聯會的方向經客戶確認（AI Buddy 可以晚一點）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
+          <t>政協青年聯會版的造型圖（正、側、背面，尺寸，顏色，材質建議）交給玩具廠；馬會兩款已交；AI Buddy 造型可以延後</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="15" t="n"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>W2–W4</t>
+          <t>W3–W5</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>11/6</t>
+          <t>11/13</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Navy → Jacky</t>
+          <t>Navy</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>快活、政協青年聯會的頁面設計稿</t>
+          <t>跟進打樣外觀</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>配網、綁定、首頁、對話、記憶、設定、語言等頁面的設計稿和切圖交給 Jacky，可以直接做進網頁；政協青年聯會版只換顏色、logo、插圖；客戶確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
+          <t>每一輪樣品都對照造型圖給外觀修改意見；11/13 簽樣時外觀和設計一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
       <c r="A7" s="15" t="n"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>10/23</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>三套 UI／UX 設計方向</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>快活、政協青年聯會、AI Buddy 各一份設計規範（顏色、字體、圖示、按鈕）和主要頁面線框；快活和政協青年聯會的方向經客戶確認（AI Buddy 可以晚一點）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>W2–W4</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>11/6</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Navy → Jacky</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>快活、政協青年聯會的頁面設計稿</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>配網、綁定、首頁、對話、記憶、設定、語言等頁面的設計稿和切圖交給 Jacky，可以直接做進網頁；政協青年聯會版只換顏色、logo、插圖；客戶確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>W2–W5</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>11/13</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Navy；Jacky 放進系統</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>角色和內容</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>快活和政協青年聯會每個角色都有人設、說話風格、開場白、聲線和角色圖；每個角色試聽 20 句，客戶確認</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="4" t="inlineStr">
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>W6–W7</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Navy → Jacky</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>提交 App 圖</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>兩個 App 的圖示、啟動畫面、商店截圖和宣傳圖，按蘋果和 Google 的尺寸交給 Jacky</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>網頁</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>W1–W3</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>統一開發一套網頁，三套外觀；App 內登入、刪除帳號</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>同一套程式碼按設定切換三套外觀（快活、政協青年聯會、AI Buddy）：顏色、字體、logo、圖示、文案；共用元件裡沒有寫死的品牌；加一套外觀不用改程式；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="4" t="inlineStr">
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>W3–W4</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>快活網頁核心：配網、綁定、角色、對話、設定</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>iPhone 和 Android 上 10 分鐘內完成藍牙配網和綁定；選角色、對話、改設定、解綁都正常</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>W4–W6</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>快活的功能開關；政協青年聯會套用外觀</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>同一套網頁裡打開快活的功能：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版用同一套成人版流程，只換外觀和角色</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>功能凍結</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>兩個品牌全流程通過：安裝 → 登入 → 配網 → 綁定 → 對話 → 解綁，iOS 和 Android 各至少兩款手機；Wi-Fi 密碼錯、玩具已被綁定、斷網時都有清楚提示</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>App 殼與上架</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>10/23</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Jacky → Neo</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Jacky 交 App 接口參數給 Neo</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>接口文件交給 Neo：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；Neo 確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>W3–W6</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Neo</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>按接口參數開發殼、出測試版</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>兩個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>W8–W9</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>12/11</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Neo（客戶提供開發者帳號）</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>提交審核、通過審核</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>11/30 提交，上架資料齊全（截圖、私隱政策、私隱標籤、審核用帳號、玩具示範影片）；12/11 前兩個 App 通過蘋果和 Google 審核</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>1/15</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Neo</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>公開上架</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>兩個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Tool call</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>W2–W3</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>10/30</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>工具清單和設計</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>1/15 只做兩個工具：調音量、結束對話，寫好觸發說法和回覆方式。其他工具（天氣、日期和節日、快活的賽事資料）上線後經伺服器更新加入</t>
         </is>
       </c>
     </row>
@@ -1757,147 +1753,147 @@
       <c r="A18" s="16" t="n"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>公開上架</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>兩個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Tool call</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>W2–W3</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>工具清單和設計</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>1/15 只做兩個工具：調音量、結束對話，寫好觸發說法和回覆方式。其他工具（天氣、日期和節日、快活的賽事資料）上線後經伺服器更新加入</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>W4–W6</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>開發和測試</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>兩個工具各用真實語音觸發 20 次，成功率 ≥ 95%；不相關的話不會誤觸發；首字延遲增加不超過 300 毫秒</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>RAG 知識庫（快活）</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>馬會提供資料；Jacky</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>收資料、入庫流程</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>馬會第一批資料已收到；入庫、版本、審批流程跑通一次</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>W5–W8</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>檢索和回答（v1 小版本）</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>v1 只放第一批馬會資料；100 條測試問題答對率 ≥ 80%；知識庫沒有的內容會說不肯定並建議查詢；問貼士、賠率、賽果預測 100% 婉拒</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>W9–W11</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>12/25</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>馬會審核；Jacky 修改</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>馬會審核 v1</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>後台管理</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>W3–W6</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>11/20</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>管理功能</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
         </is>
       </c>
     </row>
@@ -1905,59 +1901,59 @@
       <c r="A23" s="16" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>W6–W8</t>
+          <t>W9–W11</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>12/4</t>
+          <t>12/25</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
+          <t>馬會審核；Jacky 修改</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>馬會審核 v1</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>後台管理</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>W3–W6</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>三個品牌各自一套系統</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>測試</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>W4–W7</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>11/27</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>全體</t>
-        </is>
-      </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>內部測試（20 台、4 週）</t>
+          <t>管理功能</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
+          <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1961,7 @@
       <c r="A25" s="16" t="n"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>W7–W8</t>
+          <t>W6–W8</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -1980,44 +1976,44 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>系統測試</t>
+          <t>三個品牌各自一套系統</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>全流程測試通過；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="56" customHeight="1">
+          <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>UAT</t>
+          <t>測試</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>W9–W10</t>
+          <t>W4–W7</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/27</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>馬會、政協青年聯會；Jacky</t>
+          <t>全體</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>客戶 UAT（用試產機和正式版 App）</t>
+          <t>內部測試（20 台、4 週）</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
+          <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
         </is>
       </c>
     </row>
@@ -2025,25 +2021,85 @@
       <c r="A27" s="16" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>12/4</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>系統測試</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>全流程測試通過；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>馬會、政協青年聯會；Jacky</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>客戶 UAT（用試產機和正式版 App）</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>上線前最後確認</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>UAT 遺留問題全部處理；正式環境凍結，只修 bug；監控和告警正常</t>
         </is>
@@ -2052,15 +2108,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A5:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>中期驗貨（12/25–26 香港假期）</t>
+          <t>第三方驗貨公司中期驗貨（12/25–26 香港假期）</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>尾期驗貨；客戶確認 App 公開日期</t>
+          <t>第三方驗貨公司尾期驗貨；客戶確認 App 公開日期</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1227,7 +1227,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="10" t="n"/>
     </row>
-    <row r="26" ht="40" customHeight="1">
+    <row r="26" ht="56" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Jacky</t>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>統籌時間表，對接玩具廠、電路板供應商和客戶；統一開發一套網頁、三套外觀（把 Navy 的設計圖做進 App 畫面）、後台、語音系統、韌體、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；負責測試和 UAT</t>
+          <t>定技術方向；開發韌體（藍牙配網、加密、按品牌連線、出廠工位）、一套網頁三套外觀、後台、語音系統、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；系統測試。與 Claude 協作，雲端的獨立工作可以開多個 session 並行做</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>IP 造型設計（政協青年聯會版等），跟進打樣外觀到簽樣；三套 UI／UX 設計；角色和內容（人設、說話風格、開場白、聲線、角色圖）；App 設計圖、圖示、啟動畫面和商店截圖，全部交給 Jacky</t>
+          <t>IP 造型設計（政協青年聯會版等），跟進打樣外觀到簽樣；三套 UI／UX 設計；角色和內容（人設、開場白、聲線、角色圖、提示語初稿）；整理馬會資料、寫 RAG 測試問題；包裝和說明書；App 設計圖、圖示、商店截圖交給 Jacky</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="10" t="n"/>
     </row>
-    <row r="28" ht="40" customHeight="1">
+    <row r="28" ht="56" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Neo</t>
@@ -1278,29 +1278,52 @@
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>App 殼</t>
+          <t>App 殼和上架</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>按 Jacky 給的接口參數，開發 iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；出測試版，提交蘋果和 Google 審核並上架</t>
+          <t>按 Jacky 給的接口參數開發 iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；手機端測試（iOS、Android 各兩款）；整個上架流程，包括跟進客戶開開發者帳號、私隱標籤、審核溝通；UAT 時的手機支援；如熟 Next.js，分擔部分網頁頁面</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="10" t="n"/>
     </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>對接人（待定）</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>對接和行政</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>建議由老闆或行政／採購同事擔任：跟進玩具廠、Spotpear 的報價、落單、交期和物流；檢測所送檢；安排第三方驗貨公司做中期和尾期驗貨；跟客戶要資料、簽樣、約 UAT；找律師起草私隱政策；內部測試機的分發和回饋；客服聯絡、常見問題、保修條款</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D26:G26"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="D25:G25"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D29:G29"/>
     <mergeCell ref="D27:G27"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="D28:G28"/>
@@ -1316,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1489,7 +1512,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="56" customHeight="1">
       <c r="A9" s="15" t="n"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -1508,100 +1531,100 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>角色和內容</t>
+          <t>角色和內容（含提示語初稿）</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>快活和政協青年聯會每個角色都有人設、說話風格、開場白、聲線和角色圖；每個角色試聽 20 句，客戶確認</t>
+          <t>快活和政協青年聯會每個角色都有人設、說話風格、開場白、聲線、角色圖，以及提示語初稿（說話規則、禁止話題）；每個角色試聽 20 句，客戶確認</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="15" t="n"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>W5–W6</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Navy → 玩具廠</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>包裝和說明書</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>彩盒、說明書（含配網步驟）、App 下載 QR 碼的設計稿交玩具廠打樣；商店描述文字交 Neo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>W6–W7</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Navy → Jacky</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>提交 App 圖</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>兩個 App 的圖示、啟動畫面、商店截圖和宣傳圖，按蘋果和 Google 的尺寸交給 Jacky</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>網頁</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>W1–W3</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>韌體</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>W2–W3</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>統一開發一套網頁，三套外觀；App 內登入、刪除帳號</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>同一套程式碼按設定切換三套外觀（快活、政協青年聯會、AI Buddy）：顏色、字體、logo、圖示、文案；共用元件裡沒有寫死的品牌；加一套外觀不用改程式；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>W3–W4</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>11/6</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>快活網頁核心：配網、綁定、角色、對話、設定</t>
+          <t>藍牙配網韌體</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>iPhone 和 Android 上 10 分鐘內完成藍牙配網和綁定；選角色、對話、改設定、解綁都正常</t>
+          <t>廣播帶品牌、回傳 Wi-Fi 清單、收密碼和綁定票、配網後釋放藍牙記憶體；手機 10 分鐘內完成配網和綁定；對話中最低可用記憶體不比現在差</t>
         </is>
       </c>
     </row>
@@ -1609,216 +1632,212 @@
       <c r="A13" s="15" t="n"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>W2–W5</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>分區表和加密</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>分區表凍結（加大 app 分區、加品牌資源分區）；一片測試板驗證 Secure Boot 和 Flash 加密：未簽名映像 OTA 被拒，讀出的 flash 是密文</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>W4–W5</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>按品牌連線</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>伺服器網址改為從出廠設定讀取；兩片板寫入不同品牌，各自連上自己那套系統；清空設定後不連任何正式伺服器</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>W5–W7</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>出廠模式和工位腳本</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>經序列埠寫入密鑰、品牌、款式，自檢，再登記到該品牌的系統；連續 10 台通過，混入壞板能攔下</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>出廠韌體定版，交 Spotpear</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>包含以上四項；Spotpear 試燒 10 片，我方驗證通過；記錄版本號。之後只能經 OTA 更新 app 部分</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>網頁</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>W1–W3</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>統一開發一套網頁，三套外觀；App 內登入、刪除帳號</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>同一套程式碼按設定切換三套外觀（快活、政協青年聯會、AI Buddy）：顏色、字體、logo、圖示、文案；共用元件裡沒有寫死的品牌；加一套外觀不用改程式；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>W3–W4</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>11/6</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>快活網頁核心：配網、綁定、角色、對話、設定</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>iPhone 和 Android 上 10 分鐘內完成藍牙配網和綁定；選角色、對話、改設定、解綁都正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>W4–W6</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>快活的功能開關；政協青年聯會套用外觀</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>同一套網頁裡打開快活的功能：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版用同一套成人版流程，只換外觀和角色</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>11/27</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>功能凍結</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>兩個品牌全流程通過：安裝 → 登入 → 配網 → 綁定 → 對話 → 解綁，iOS 和 Android 各至少兩款手機；Wi-Fi 密碼錯、玩具已被綁定、斷網時都有清楚提示</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>App 殼與上架</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>W1–W2</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>10/23</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Jacky → Neo</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Jacky 交 App 接口參數給 Neo</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>接口文件交給 Neo：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；Neo 確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>W3–W6</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>11/20</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Neo</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>按接口參數開發殼、出測試版</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>兩個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="56" customHeight="1">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>W8–W9</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>12/11</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Neo（客戶提供開發者帳號）</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>提交審核、通過審核</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>11/30 提交，上架資料齊全（截圖、私隱政策、私隱標籤、審核用帳號、玩具示範影片）；12/11 前兩個 App 通過蘋果和 Google 審核</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>1/15</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Neo</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>公開上架</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>兩個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Tool call</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>W2–W3</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>10/30</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>工具清單和設計</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>1/15 只做兩個工具：調音量、結束對話，寫好觸發說法和回覆方式。其他工具（天氣、日期和節日、快活的賽事資料）上線後經伺服器更新加入</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
+    <row r="20" ht="56" customHeight="1">
       <c r="A20" s="16" t="n"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>W4–W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>11/27</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1828,44 +1847,44 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>開發和測試</t>
+          <t>功能凍結</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>兩個工具各用真實語音觸發 20 次，成功率 ≥ 95%；不相關的話不會誤觸發；首字延遲增加不超過 300 毫秒</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
+          <t>兩個品牌全流程通過：安裝 → 登入 → 配網 → 綁定 → 對話 → 解綁，iOS 和 Android 各至少兩款手機；Wi-Fi 密碼錯、玩具已被綁定、斷網時都有清楚提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>RAG 知識庫（快活）</t>
+          <t>App 殼與上架</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W1–W2</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>11/6</t>
+          <t>10/23</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>馬會提供資料；Jacky</t>
+          <t>Jacky → Neo</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>收資料、入庫流程</t>
+          <t>Jacky 交 App 接口參數給 Neo</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>馬會第一批資料已收到；入庫、版本、審批流程跑通一次</t>
+          <t>接口文件交給 Neo：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；Neo 確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
         </is>
       </c>
     </row>
@@ -1873,207 +1892,203 @@
       <c r="A22" s="15" t="n"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>W3–W6</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>按接口參數開發殼、出測試版</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>兩個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>W8–W9</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>12/11</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Neo（跟進客戶開帳號、上架資料）</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>提交審核、通過審核</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>11/30 提交，上架資料齊全（截圖、私隱政策、私隱標籤、審核用帳號、玩具示範影片）；12/11 前兩個 App 通過蘋果和 Google 審核</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>公開上架</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>兩個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Tool call</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>W2–W3</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>工具清單和設計</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>1/15 只做兩個工具：調音量、結束對話，寫好觸發說法和回覆方式。其他工具（天氣、日期和節日、快活的賽事資料）上線後經伺服器更新加入</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>W4–W6</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>開發和測試</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>兩個工具各用真實語音觸發 20 次，成功率 ≥ 95%；不相關的話不會誤觸發；首字延遲增加不超過 300 毫秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>RAG 知識庫（快活）</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>11/6</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>馬會提供資料；Navy 整理；Jacky 入庫</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>收資料、整理、入庫</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>馬會第一批資料已收到；Navy 整理成問答，並寫好 100 條測試問題和標準答案；入庫、版本、審批流程跑通一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>W5–W8</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>檢索和回答（v1 小版本）</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>v1 只放第一批馬會資料；100 條測試問題答對率 ≥ 80%；知識庫沒有的內容會說不肯定並建議查詢；問貼士、賠率、賽果預測 100% 婉拒</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>W9–W11</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>12/25</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>馬會審核；Jacky 修改</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>馬會審核 v1</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>後台管理</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>W3–W6</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>11/20</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>管理功能</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>W6–W8</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>12/4</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>三個品牌各自一套系統</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>測試</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>W4–W7</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>11/27</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>全體</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>內部測試（20 台、4 週）</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>W7–W8</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>12/4</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>系統測試</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>全流程測試通過；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>W9–W10</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>12/18</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>馬會、政協青年聯會；Jacky</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>客戶 UAT（用試產機和正式版 App）</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
         </is>
       </c>
     </row>
@@ -2081,42 +2096,223 @@
       <c r="A29" s="16" t="n"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>W9–W11</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>12/25</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>馬會審核；Jacky 修改</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>馬會審核 v1</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>後台管理</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>W3–W6</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>管理功能</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>W6–W8</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>12/4</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>三個品牌各自一套系統</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>測試</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>W4–W7</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>全體</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>內部測試（20 台、4 週）</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>12/4</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Jacky；Neo 測手機端</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>系統測試</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>全流程測試通過（Neo 用 iOS、Android 各兩款手機跑）；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>對接人約客戶；Jacky、Neo 支援</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>客戶 UAT（用試產機和正式版 App）</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>上線前最後確認</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>UAT 遺留問題全部處理；正式環境凍結，只修 bug；監控和告警正常</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A5:A10"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A5:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -1227,7 +1227,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="10" t="n"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Jacky</t>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>定技術方向；開發韌體（藍牙配網、加密、按品牌連線、出廠工位）、一套網頁三套外觀、後台、語音系統、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；系統測試。與 Claude 協作，雲端的獨立工作可以開多個 session 並行做</t>
+          <t>定技術方向；開發韌體（藍牙配網、加密、按品牌連線、出廠工位）、一套網頁三套外觀、後台、語音系統、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；系統測試</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -1269,7 +1269,7 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="10" t="n"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Neo</t>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>按 Jacky 給的接口參數開發 iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；手機端測試（iOS、Android 各兩款）；整個上架流程，包括跟進客戶開開發者帳號、私隱標籤、審核溝通；UAT 時的手機支援；如熟 Next.js，分擔部分網頁頁面</t>
+          <t>按 Jacky 給的接口參數開發 iOS 和 Android 原生殼（藍牙配網、原生登入、推送）；手機端測試（iOS、Android 各兩款）；整個上架流程，包括跟進客戶開開發者帳號、私隱標籤、審核溝通；UAT 時的手機支援</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -1339,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="56" customHeight="1">
       <c r="A15" s="15" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>經序列埠寫入密鑰、品牌、款式，自檢，再登記到該品牌的系統；連續 10 台通過，混入壞板能攔下</t>
+          <t>經序列埠寫入密鑰、品牌、款式，自檢，再按 MAC 登記 ip_key 和該 IP 的預設角色；IP 不寫進共用韌體；連續 10 台、至少兩種 IP 通過，混入壞板能攔下</t>
         </is>
       </c>
     </row>
@@ -1819,100 +1819,100 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>公仔鎖死在自己的 IP</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>出廠登記的 ip_key 決定這隻公仔；認領和 My Devices 顯示該 IP 頭像；一個帳號可同時綁兩種公仔，各只能選自己 IP 的角色；別的 IP 的角色寫不進這台</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>W4–W6</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
           <t>快活的功能開關；政協青年聯會套用外觀</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>同一套網頁裡打開快活的功能：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版用同一套成人版流程，只換外觀和角色</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>功能凍結</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>兩個品牌全流程通過：安裝 → 登入 → 配網 → 綁定 → 對話 → 解綁，iOS 和 Android 各至少兩款手機；Wi-Fi 密碼錯、玩具已被綁定、斷網時都有清楚提示</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>App 殼與上架</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>W1–W2</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>10/23</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Jacky → Neo</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Jacky 交 App 接口參數給 Neo</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>接口文件交給 Neo：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；Neo 確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>W3–W6</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>11/20</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Neo</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>按接口參數開發殼、出測試版</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>兩個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
         </is>
       </c>
     </row>
@@ -1920,381 +1920,409 @@
       <c r="A23" s="15" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>W3–W6</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>按接口參數開發殼、出測試版</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>兩個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>W8–W9</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>12/11</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Neo（跟進客戶開帳號、上架資料）</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>提交審核、通過審核</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>11/30 提交，上架資料齊全（截圖、私隱政策、私隱標籤、審核用帳號、玩具示範影片）；12/11 前兩個 App 通過蘋果和 Google 審核</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>1/15</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Neo</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>公開上架</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>兩個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Tool call</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>W2–W3</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>工具清單和設計</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>1/15 只做兩個工具：調音量、結束對話，寫好觸發說法和回覆方式。其他工具（天氣、日期和節日、快活的賽事資料）上線後經伺服器更新加入</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="4" t="inlineStr">
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>W4–W6</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>開發和測試</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>兩個工具各用真實語音觸發 20 次，成功率 ≥ 95%；不相關的話不會誤觸發；首字延遲增加不超過 300 毫秒</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="72" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>RAG 知識庫（快活）</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>馬會提供資料；Navy 整理；Jacky 入庫</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>收資料、整理、入庫</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>馬會第一批資料已收到；Navy 整理成問答，並寫好 100 條測試問題和標準答案；入庫、版本、審批流程跑通一次</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="4" t="inlineStr">
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>W5–W8</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>檢索和回答（v1 小版本）</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>v1 只放第一批馬會資料；100 條測試問題答對率 ≥ 80%；知識庫沒有的內容會說不肯定並建議查詢；問貼士、賠率、賽果預測 100% 婉拒</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>W9–W11</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>12/25</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>馬會審核；Jacky 修改</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>馬會審核 v1</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>後台管理</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>W3–W6</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>管理功能</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>W6–W8</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>三個品牌各自一套系統</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>測試</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>W4–W7</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>全體</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>內部測試（20 台、4 週）</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>W7–W8</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>12/4</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Jacky；Neo 測手機端</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>系統測試</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>全流程測試通過（Neo 用 iOS、Android 各兩款手機跑）；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>UAT</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>W9–W10</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>12/18</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>對接人約客戶；Jacky、Neo 支援</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>客戶 UAT（用試產機和正式版 App）</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Jacky</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>上線前最後確認</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>UAT 遺留問題全部處理；正式環境凍結，只修 bug；監控和告警正常</t>
         </is>
@@ -2302,16 +2330,16 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A17:A21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A22:A25"/>
     <mergeCell ref="A5:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.6.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Navy 完成政協青年聯會版的 IP 造型設計，交玩具廠（馬會的已交）；交機芯規格；向電路板供應商詢價、追加樣板</t>
+          <t>設計負責人（待定）完成政協青年聯會版的 IP 造型設計，交玩具廠（馬會的已交）；交機芯規格；向電路板供應商詢價、追加樣板</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1">
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>W2</t>
@@ -715,12 +715,12 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>審 3D 圖；決定電路板改不改；Jacky 把 App 接口參數交給 Neo；Navy 出 UI／UX 設計方向</t>
+          <t>審 3D 圖；決定電路板改不改；Jacky 把 App 接口參數交給 App 殼負責人（待定）；設計負責人（待定）出 UI／UX 設計方向</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；接口參數 Neo 確認可以開發；設計方向交客戶</t>
+          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；接口參數 App 殼負責人（待定）確認可以開發；設計方向交客戶</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>裝板實測，給修改意見；Navy 給外觀意見；電路板定案；App 登入和品牌主題</t>
+          <t>裝板實測，給修改意見；設計負責人（待定）給外觀意見；電路板定案；App 登入和品牌主題</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>交燒錄自檢工位和作業指導書；Neo 提交兩個 App 給蘋果和 Google 審核；系統測試</t>
+          <t>交燒錄自檢工位和作業指導書；App 殼負責人（待定）提交兩個 App 給蘋果和 Google 審核；系統測試</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>定技術方向；開發韌體（藍牙配網、加密、按品牌連線、出廠工位）、一套網頁三套外觀、後台、語音系統、Tool call 和 RAG，部署三套系統；給 Neo App 接口參數；系統測試</t>
+          <t>定技術方向；開發韌體（藍牙配網、加密、按品牌連線、出廠工位）、一套網頁三套外觀、後台、語音系統、Tool call 和 RAG，部署三套系統；把 App 接口參數交給 App 殼負責人（待定）；系統測試</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
@@ -1272,7 +1272,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="B28" s="10" t="n"/>
@@ -1360,7 +1360,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>網頁統一開發一套，三個品牌是三套外觀，包在原生殼裡；1/15 上架快活和政協青年聯會兩個 App（AI Buddy 隨玩具延後）。殼由 Neo 負責；設計、角色和 App 圖由 Navy 負責；網頁、後台、語音系統和韌體由 Jacky 負責。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
+          <t>網頁統一開發一套，三個品牌是三套外觀，包在原生殼裡；1/15 上架快活和政協青年聯會兩個 App（AI Buddy 隨玩具延後）。殼的負責人待定；設計、角色和 App 圖的負責人待定；網頁、後台、語音系統和韌體由 Jacky 負責。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Navy → 玩具廠</t>
+          <t>待定 → 玩具廠</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Navy → Jacky</t>
+          <t>待定 → Jacky</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Navy；Jacky 放進系統</t>
+          <t>待定；Jacky 放進系統</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Navy → 玩具廠</t>
+          <t>待定 → 玩具廠</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>彩盒、說明書（含配網步驟）、App 下載 QR 碼的設計稿交玩具廠打樣；商店描述文字交 Neo</t>
+          <t>彩盒、說明書（含配網步驟）、App 下載 QR 碼的設計稿交玩具廠打樣；商店描述文字交 App 殼負責人（待定）</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Navy → Jacky</t>
+          <t>待定 → Jacky</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Jacky → Neo</t>
+          <t>Jacky → 待定</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Jacky 交 App 接口參數給 Neo</t>
+          <t>Jacky 交 App 接口參數給 App 殼負責人（待定）</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>接口文件交給 Neo：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；Neo 確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
+          <t>接口文件交給 App 殼負責人（待定）：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明參數、回傳和錯誤；App 殼負責人（待定）確認看得懂、可以開發；兩個 App 的名稱、圖示、bundle id 定好</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Neo（跟進客戶開帳號、上架資料）</t>
+          <t>待定（跟進客戶開帳號、上架資料）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>馬會提供資料；Navy 整理；Jacky 入庫</t>
+          <t>馬會提供資料；待定整理；Jacky 入庫</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>馬會第一批資料已收到；Navy 整理成問答，並寫好 100 條測試問題和標準答案；入庫、版本、審批流程跑通一次</t>
+          <t>馬會第一批資料已收到；設計負責人（待定）整理成問答，並寫好 100 條測試問題和標準答案；入庫、版本、審批流程跑通一次</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Jacky；Neo 測手機端</t>
+          <t>Jacky；待定測手機端</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>全流程測試通過（Neo 用 iOS、Android 各兩款手機跑）；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
+          <t>全流程測試通過（App 殼負責人（待定）用 iOS、Android 各兩款手機跑）；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>對接人約客戶；Jacky、Neo 支援</t>
+          <t>對接人約客戶；Jacky、待定支援</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
